--- a/llm-benchmark/data/sample_absa.xlsx
+++ b/llm-benchmark/data/sample_absa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="94">
   <si>
     <t>title</t>
   </si>
@@ -85,45 +85,48 @@
     <t>News18</t>
   </si>
   <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>AIADMK vs DMK direct contest in fewer seats in 2026 polls - The New Indian Express</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNR2Utc0NRRkg0ZlZabkFveFVITE1BOFg3ek9oNExkVnNVeEdLcmViS20wUWwzcEtpNUZQRlFtZ1pLaWExNktZRUVJZkxIZkZKVk5UX0FRWlNmdjV3cnRLMkdxdl9CY0ZRM2lQaW5MT0Y5WVQzVUgxR282anRBX3BzVXUyRVlDS21mYV81RlN0NTVzYVpYU2hjVnlsVkx6OUZHN0g1bU9LSGVJb3lLc3FQeG5B0gG_AUFVX3lxTFAwaHBwR3VWNFRSb2FGVjBfYlU2ZVpkd2hwSWxYOUlXN1BOeTBtc1BaU0N5TVIwTEVSN3BxTFVqQ2VPa1hLSFUwbDRzbDNwWWJ3TjIxemY5VnJpdlhTNFRfY3M0M05xXzAyQzdJRTVySmhfME1kVlJEWS13U3Z0X3h0UThSNEtFaGFsMkw0djVMdUh0TllRVGRZUXNaZmM0WUgtcFUwMG90Mm5ybFhrTm95Y0VpUF90dEVDOVZ1bUdz?oc=5</t>
+  </si>
+  <si>
+    <t>Tue, 31 Mar 2026 02:34:41 GMT</t>
+  </si>
+  <si>
+    <t>The New Indian Express</t>
+  </si>
+  <si>
+    <t>Tamil Nadu Assembly 2026: AIADMK-BJP 'Delhi-made' Row, DMK Manifesto - Deccan Herald</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdkN6LUlGeXItdExYalN5RzZnQWhaUkdtZkFYUDlLSndiT1lGQUhwOFpCRWFaeElGN1NpbFhmZjVIdU9XbUU2R05tVnRiek0xeC0wQ2dVMjhyaFJNNmZ4ZlNKOTcyaDB5UVFlclJldl94cWczTW5wanVOeTFuSnJtZ0hwZllkX1QzVFNhd3lId2NNTXpDYjd6MmF6RHdLOU5NMEJSZlBBQWhkLWE5Ul9udDlKbE9EVG4yNXl6UmhObnVVOUFOMExDakVwZWo1U1ZsR1RPYW15amE3Rlh4WU53UHFHQmpCSTZlWXU2VmhnQkFPZXMxeERYQlJYeE96VDFLNVE?oc=5</t>
+  </si>
+  <si>
+    <t>Tue, 31 Mar 2026 04:50:08 GMT</t>
+  </si>
+  <si>
+    <t>Deccan Herald</t>
+  </si>
+  <si>
+    <t>AIADMK will push for lowering GST for match industry, assures Palaniswami - The Siasat Daily</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeWFvTGFROEJ0WHpRUnhiYmlHZk1WWW9iSGdxWkZGRjV5Zk56eERGVzVpd1I3YWFkLU5vcTFWd1loTE82UUIyQTlLeTNBQzlieEJWeGNGWURiQm5SMDBKakhvYVhXVExxS2o0QzJyd0x3X2E1VlZKU1lLUS1hc0sxNHNxTmpyRExISm03dEtmVUx1S2dBWnVISEROVEpzVmJvZUhxV3RSa9IBrAFBVV95cUxPd1lyeEo0bHh5TnJsSVpsc3g5eXdQZmRGU3l5dkdhM2ZSeXprLVJrX28xaDRnYzVOU015bEw1Rm90MHEwQ2xKMm90WXVYS1A4amtSeU9seXpoSWgydlFKbUNpOHluWEtvc1EwRFdGaThKazR5MkhZQmtsWTNMeW9RYkYwbEZ3dW9laGczcThZaDNIeUJZeGliSlFnVWdnaGl0TDdvbWtyckdhY1NI?oc=5</t>
+  </si>
+  <si>
+    <t>Tue, 31 Mar 2026 06:47:00 GMT</t>
+  </si>
+  <si>
+    <t>The Siasat Daily</t>
+  </si>
+  <si>
     <t>Positive</t>
   </si>
   <si>
-    <t>AIADMK vs DMK direct contest in fewer seats in 2026 polls - The New Indian Express</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNR2Utc0NRRkg0ZlZabkFveFVITE1BOFg3ek9oNExkVnNVeEdLcmViS20wUWwzcEtpNUZQRlFtZ1pLaWExNktZRUVJZkxIZkZKVk5UX0FRWlNmdjV3cnRLMkdxdl9CY0ZRM2lQaW5MT0Y5WVQzVUgxR282anRBX3BzVXUyRVlDS21mYV81RlN0NTVzYVpYU2hjVnlsVkx6OUZHN0g1bU9LSGVJb3lLc3FQeG5B0gG_AUFVX3lxTFAwaHBwR3VWNFRSb2FGVjBfYlU2ZVpkd2hwSWxYOUlXN1BOeTBtc1BaU0N5TVIwTEVSN3BxTFVqQ2VPa1hLSFUwbDRzbDNwWWJ3TjIxemY5VnJpdlhTNFRfY3M0M05xXzAyQzdJRTVySmhfME1kVlJEWS13U3Z0X3h0UThSNEtFaGFsMkw0djVMdUh0TllRVGRZUXNaZmM0WUgtcFUwMG90Mm5ybFhrTm95Y0VpUF90dEVDOVZ1bUdz?oc=5</t>
-  </si>
-  <si>
-    <t>Tue, 31 Mar 2026 02:34:41 GMT</t>
-  </si>
-  <si>
-    <t>The New Indian Express</t>
-  </si>
-  <si>
-    <t>Tamil Nadu Assembly 2026: AIADMK-BJP 'Delhi-made' Row, DMK Manifesto - Deccan Herald</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdkN6LUlGeXItdExYalN5RzZnQWhaUkdtZkFYUDlLSndiT1lGQUhwOFpCRWFaeElGN1NpbFhmZjVIdU9XbUU2R05tVnRiek0xeC0wQ2dVMjhyaFJNNmZ4ZlNKOTcyaDB5UVFlclJldl94cWczTW5wanVOeTFuSnJtZ0hwZllkX1QzVFNhd3lId2NNTXpDYjd6MmF6RHdLOU5NMEJSZlBBQWhkLWE5Ul9udDlKbE9EVG4yNXl6UmhObnVVOUFOMExDakVwZWo1U1ZsR1RPYW15amE3Rlh4WU53UHFHQmpCSTZlWXU2VmhnQkFPZXMxeERYQlJYeE96VDFLNVE?oc=5</t>
-  </si>
-  <si>
-    <t>Tue, 31 Mar 2026 04:50:08 GMT</t>
-  </si>
-  <si>
-    <t>Deccan Herald</t>
-  </si>
-  <si>
-    <t>AIADMK will push for lowering GST for match industry, assures Palaniswami - The Siasat Daily</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeWFvTGFROEJ0WHpRUnhiYmlHZk1WWW9iSGdxWkZGRjV5Zk56eERGVzVpd1I3YWFkLU5vcTFWd1loTE82UUIyQTlLeTNBQzlieEJWeGNGWURiQm5SMDBKakhvYVhXVExxS2o0QzJyd0x3X2E1VlZKU1lLUS1hc0sxNHNxTmpyRExISm03dEtmVUx1S2dBWnVISEROVEpzVmJvZUhxV3RSa9IBrAFBVV95cUxPd1lyeEo0bHh5TnJsSVpsc3g5eXdQZmRGU3l5dkdhM2ZSeXprLVJrX28xaDRnYzVOU015bEw1Rm90MHEwQ2xKMm90WXVYS1A4amtSeU9seXpoSWgydlFKbUNpOHluWEtvc1EwRFdGaThKazR5MkhZQmtsWTNMeW9RYkYwbEZ3dW9laGczcThZaDNIeUJZeGliSlFnVWdnaGl0TDdvbWtyckdhY1NI?oc=5</t>
-  </si>
-  <si>
-    <t>Tue, 31 Mar 2026 06:47:00 GMT</t>
-  </si>
-  <si>
-    <t>The Siasat Daily</t>
-  </si>
-  <si>
     <t>AIADMK announces second list of party candidates for TN Assembly polls - MSN</t>
   </si>
   <si>
@@ -143,9 +146,6 @@
   </si>
   <si>
     <t>Mon, 30 Mar 2026 15:45:17 GMT</t>
-  </si>
-  <si>
-    <t>Neutral</t>
   </si>
   <si>
     <t>Wife of late Valparai MLA quits AIADMK, joins NTK - The New Indian Express</t>
@@ -374,15 +374,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -690,17 +696,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
+    <col min="7" max="7" style="5" width="98.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -725,631 +732,672 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I5" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>23</v>
+      <c r="H7" s="2"/>
+      <c r="I7" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>36</v>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I8" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>40</v>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I11" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I12" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>43</v>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>43</v>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>23</v>
+      <c r="H22" s="2"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="D23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="D24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>23</v>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="D25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="2"/>
+      <c r="I25" s="3" t="s">
         <v>14</v>
       </c>
     </row>
